--- a/feedback_forms/004_local_business_review_request--feedback_forms.xlsx
+++ b/feedback_forms/004_local_business_review_request--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>form category</t>
+          <t>Form Category 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_output_file</t>
+          <t>form_output_file_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>form output file</t>
+          <t>Form Output File 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_assigned_tool</t>
+          <t>form_assigned_tool_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>form assigned tool</t>
+          <t>Form Assigned Tool 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_form_title</t>
+          <t>form_form_title_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>form form title</t>
+          <t>Form Form Title 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feedback_forms</t>
+          <t>feedback forms</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feedback_forms</t>
+          <t>feedback forms</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1374,14 +1374,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feedback_forms</t>
+          <t>feedback forms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_assigned_tool_choices</t>
+          <t>form_assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_assigned_tool_choices</t>
+          <t>form_assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
